--- a/database/Mater_issue_out.xlsx
+++ b/database/Mater_issue_out.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2882114-71C9-4866-BB02-805907DB1BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7D9D3-6682-4FB4-8410-59CD063EE169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_ACC_Master" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="189">
   <si>
     <t>TypeID</t>
   </si>
@@ -262,12 +262,6 @@
     <t>Hàng mua từ vendor nhưng NG do bên vận chuyển, đòi tiền bên vận chuyển</t>
   </si>
   <si>
-    <t>5.Disposition</t>
-  </si>
-  <si>
-    <t>Hàng NVL hủy do PSNV chịu chi phí</t>
-  </si>
-  <si>
     <t>6.Claim Scrap Halb</t>
   </si>
   <si>
@@ -325,27 +319,12 @@
     <t>Issue NVL phụ cho tiêu dùng nội bộ</t>
   </si>
   <si>
-    <t>15.Post Difference End Of Month</t>
-  </si>
-  <si>
     <t>Post difference giữa tồn kho thực tế và hệ thống</t>
   </si>
   <si>
-    <t>16.Post Difference Outsourcing</t>
-  </si>
-  <si>
-    <t>Post difference giữa tồn kho thực tế và hệ thống của kho nhà thầu phụ</t>
-  </si>
-  <si>
-    <t>17.Production Rejects</t>
-  </si>
-  <si>
     <t>Hàng hỏng do sản xuất</t>
   </si>
   <si>
-    <t>18.Production Rejects for Outsourcing</t>
-  </si>
-  <si>
     <t>Hàng hỏng do sản xuất của kho nhà thầu phụ</t>
   </si>
   <si>
@@ -575,6 +554,60 @@
   </si>
   <si>
     <t>vanhuong.nguyen@vn.panasonic.com</t>
+  </si>
+  <si>
+    <t>Claim Scrap Material (Claim transportation company</t>
+  </si>
+  <si>
+    <t>5.1DispositionHalb</t>
+  </si>
+  <si>
+    <t>Hàng NVL hủy do PSNV chịu chi phí (Halb)</t>
+  </si>
+  <si>
+    <t>Scrap (Halb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1Post Difference OutsourcingHalb </t>
+  </si>
+  <si>
+    <t>Post difference giữa tồn kho thực tế và hệ thống c</t>
+  </si>
+  <si>
+    <t>5.2DispositionRoh</t>
+  </si>
+  <si>
+    <t>Hàng NVL hủy do PSNV chịu chi phí (Roh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2Post Difference OutsourcingRoh </t>
+  </si>
+  <si>
+    <t>Loss/Gain Inventory Differences (Roh)</t>
+  </si>
+  <si>
+    <t>15.1Post Difference End Of MonthHalb</t>
+  </si>
+  <si>
+    <t>15.2Post Difference End Of MonthHalb</t>
+  </si>
+  <si>
+    <t>18.1Production Rejects for OutsourcingHalb</t>
+  </si>
+  <si>
+    <t>Direct Material Cost Reject (Halb)</t>
+  </si>
+  <si>
+    <t>18.2Production Rejects for OutsourcingRoh</t>
+  </si>
+  <si>
+    <t>Direct Material Cost Reject (Roh)</t>
+  </si>
+  <si>
+    <t>17.1Production RejectsHalb</t>
+  </si>
+  <si>
+    <t>17.2Production RejectsRoh</t>
   </si>
 </sst>
 </file>
@@ -1834,10 +1867,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E041C3-B346-4B6E-B61E-D7486518563F}">
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultColWidth="18.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
+    <col min="9" max="9" width="54.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1859,8 +1903,17 @@
       <c r="G1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1882,8 +1935,17 @@
       <c r="G2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>6210211000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1902,8 +1964,17 @@
       <c r="G3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>6210140000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1922,8 +1993,17 @@
       <c r="G4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>6210300000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1942,8 +2022,17 @@
       <c r="G5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>6210140000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1965,16 +2054,25 @@
       <c r="G6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>8110110000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>171</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -1988,39 +2086,57 @@
       <c r="G7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>6210010000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>174</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6210110000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2034,62 +2150,89 @@
       <c r="G9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>8110110000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <v>8110110000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>8110110000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2103,82 +2246,118 @@
       <c r="G12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <v>6210300000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>8110110000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>6210160000</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>84</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>85</v>
       </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>8110110000</v>
+      </c>
+      <c r="I15" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -2195,13 +2374,22 @@
       <c r="G16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <v>8110110000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
@@ -2218,13 +2406,22 @@
       <c r="G17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <v>8110110000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -2241,16 +2438,25 @@
       <c r="G18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <v>6210211000</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -2264,16 +2470,25 @@
       <c r="G19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <v>6210211000</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -2287,22 +2502,31 @@
       <c r="G20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <v>6210210000</v>
+      </c>
+      <c r="I20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
         <v>32</v>
@@ -2310,16 +2534,25 @@
       <c r="G21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <v>6210020000</v>
+      </c>
+      <c r="I21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -2333,16 +2566,25 @@
       <c r="G22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <v>6210120000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>180</v>
+      </c>
+      <c r="J22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -2356,16 +2598,25 @@
       <c r="G23" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <v>6210020000</v>
+      </c>
+      <c r="I23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -2379,16 +2630,25 @@
       <c r="G24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <v>6210120000</v>
+      </c>
+      <c r="I24" t="s">
+        <v>180</v>
+      </c>
+      <c r="J24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -2402,68 +2662,95 @@
       <c r="G25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <v>6210030000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
       </c>
       <c r="E26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26">
+        <v>6210130000</v>
+      </c>
+      <c r="I26" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
         <v>68</v>
       </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>22</v>
-      </c>
-      <c r="B27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
       <c r="F27" t="s">
         <v>32</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <v>6210030000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2471,16 +2758,25 @@
       <c r="G28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <v>6210130000</v>
+      </c>
+      <c r="I28" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -2494,16 +2790,25 @@
       <c r="G29" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <v>6210300000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -2516,6 +2821,175 @@
       </c>
       <c r="G30" t="s">
         <v>7</v>
+      </c>
+      <c r="H30">
+        <v>6418000000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31">
+        <v>8110110000</v>
+      </c>
+      <c r="I31" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>6418000000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>6210131000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>6210131000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>6210210000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2536,10 +3010,10 @@
         <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2550,10 +3024,10 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2561,10 +3035,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2582,7 +3056,7 @@
         <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
         <v>38</v>
@@ -2623,10 +3097,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
         <v>52</v>
@@ -2635,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I2" t="s">
         <v>54</v>
@@ -2658,10 +3132,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
@@ -2670,7 +3144,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I3" t="s">
         <v>54</v>
@@ -2693,10 +3167,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F4" t="s">
         <v>52</v>
@@ -2705,7 +3179,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
         <v>54</v>
@@ -2722,25 +3196,25 @@
         <v>2327</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s">
         <v>54</v>
@@ -2757,25 +3231,25 @@
         <v>2328</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I6" t="s">
         <v>54</v>
@@ -2792,25 +3266,25 @@
         <v>2329</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I7" t="s">
         <v>54</v>
@@ -2833,19 +3307,19 @@
         <v>2007600</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I8" t="s">
         <v>54</v>
@@ -2862,16 +3336,16 @@
         <v>2430</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
         <v>52</v>
@@ -2880,10 +3354,10 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I9" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J9" s="1">
         <v>44734.535416666666</v>
@@ -2897,28 +3371,28 @@
         <v>2433</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I10" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J10" s="1">
         <v>44734.535416666666</v>
@@ -2932,28 +3406,28 @@
         <v>2434</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J11" s="1">
         <v>44734.535416666666</v>
@@ -2967,28 +3441,28 @@
         <v>2435</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J12" s="1">
         <v>44734.535416666666</v>
@@ -3008,16 +3482,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E14" s="1"/>
     </row>
@@ -3026,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
         <v>54</v>
@@ -3049,19 +3523,19 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
         <v>54</v>
@@ -3084,19 +3558,19 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
         <v>54</v>
@@ -3119,19 +3593,19 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
         <v>54</v>
@@ -3154,19 +3628,19 @@
         <v>123456</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
         <v>54</v>
@@ -3189,10 +3663,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
         <v>52</v>
@@ -3201,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
         <v>54</v>
@@ -3224,19 +3698,19 @@
         <v>123456</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I21" t="s">
         <v>54</v>
@@ -3259,19 +3733,19 @@
         <v>123456</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
         <v>54</v>
@@ -3294,19 +3768,19 @@
         <v>123456</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I23" t="s">
         <v>54</v>
@@ -3329,19 +3803,19 @@
         <v>123456</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -3364,19 +3838,19 @@
         <v>123456</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I25" t="s">
         <v>54</v>
@@ -3399,19 +3873,19 @@
         <v>123456</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I26" t="s">
         <v>54</v>
@@ -3434,19 +3908,19 @@
         <v>123456</v>
       </c>
       <c r="D27" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I27" t="s">
         <v>54</v>
@@ -3469,19 +3943,19 @@
         <v>123456</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I28" t="s">
         <v>54</v>
@@ -3504,19 +3978,19 @@
         <v>123456</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I29" t="s">
         <v>54</v>
@@ -3539,19 +4013,19 @@
         <v>123456</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I30" t="s">
         <v>54</v>
@@ -3574,19 +4048,19 @@
         <v>123456</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I31" t="s">
         <v>54</v>
@@ -3609,19 +4083,19 @@
         <v>123456</v>
       </c>
       <c r="D32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G32">
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I32" t="s">
         <v>54</v>

--- a/database/Mater_issue_out.xlsx
+++ b/database/Mater_issue_out.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ecom\Ecome\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7D9D3-6682-4FB4-8410-59CD063EE169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF66262-C1FD-41F0-AE8E-2723DE40E8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_ACC_Master" sheetId="1" r:id="rId1"/>
     <sheet name="tbl_Material_PriceSAP" sheetId="2" r:id="rId2"/>
     <sheet name="tbl_UserStock_IssueMaterial" sheetId="3" r:id="rId3"/>
     <sheet name="tbl_TypeMater" sheetId="4" r:id="rId4"/>
-    <sheet name="tbl_User_checkPrice" sheetId="5" r:id="rId5"/>
-    <sheet name="tbl_UserIssueRQ" sheetId="6" r:id="rId6"/>
+    <sheet name="tbl_UserDeptCombine" sheetId="7" r:id="rId5"/>
+    <sheet name="tbl_User_checkPrice" sheetId="5" r:id="rId6"/>
+    <sheet name="tbl_UserIssueRQ" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -32,16 +33,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="195">
   <si>
     <t>TypeID</t>
   </si>
@@ -608,13 +610,31 @@
   </si>
   <si>
     <t>17.2Production RejectsRoh</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Deptcombine</t>
+  </si>
+  <si>
+    <t>Level_dept</t>
+  </si>
+  <si>
+    <t>Flagdelete</t>
+  </si>
+  <si>
+    <t>Approved IT, PUR</t>
+  </si>
+  <si>
+    <t>('IT','PUR')</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -981,9 +1001,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0005190C-12A7-4AA2-B050-D4F6E798108D}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +1023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1023,7 +1043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1043,7 +1063,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1063,7 +1083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1083,7 +1103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1103,7 +1123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1123,7 +1143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1143,7 +1163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1163,7 +1183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1183,7 +1203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1203,7 +1223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1223,7 +1243,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1243,7 +1263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1263,7 +1283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1283,7 +1303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1303,7 +1323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1323,7 +1343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1343,7 +1363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1363,7 +1383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1383,7 +1403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1403,7 +1423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1423,7 +1443,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1443,7 +1463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1463,7 +1483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1491,9 +1511,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D651F0-8ED1-4701-BA6C-A1B31C35D92D}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1531,7 +1551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1569,7 +1589,7 @@
         <v>46037.427551967594</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1607,7 +1627,7 @@
         <v>46037.427552083333</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1653,9 +1673,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C07CBFB-1FCE-49A5-A1BD-2708DE2D3132}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1696,7 +1716,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>176</v>
       </c>
@@ -1737,7 +1757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>177</v>
       </c>
@@ -1778,7 +1798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>178</v>
       </c>
@@ -1819,7 +1839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>179</v>
       </c>
@@ -1868,20 +1888,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E041C3-B346-4B6E-B61E-D7486518563F}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="18.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="18.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" customWidth="1"/>
-    <col min="9" max="9" width="54.85546875" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="15.25" customWidth="1"/>
+    <col min="6" max="6" width="8.75" customWidth="1"/>
+    <col min="7" max="7" width="7.875" customWidth="1"/>
+    <col min="9" max="9" width="54.875" customWidth="1"/>
+    <col min="10" max="10" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1945,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1974,7 +1994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2003,7 +2023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2032,7 +2052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2064,7 +2084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2096,7 +2116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2128,7 +2148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2160,7 +2180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2192,7 +2212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>8</v>
       </c>
@@ -2224,7 +2244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2256,7 +2276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>10</v>
       </c>
@@ -2288,7 +2308,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>11</v>
       </c>
@@ -2320,7 +2340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>12</v>
       </c>
@@ -2352,7 +2372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>13</v>
       </c>
@@ -2384,7 +2404,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>13</v>
       </c>
@@ -2416,7 +2436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>13</v>
       </c>
@@ -2448,7 +2468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>13</v>
       </c>
@@ -2480,7 +2500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>14</v>
       </c>
@@ -2512,7 +2532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>15</v>
       </c>
@@ -2544,7 +2564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>15</v>
       </c>
@@ -2576,7 +2596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>16</v>
       </c>
@@ -2608,7 +2628,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>16</v>
       </c>
@@ -2640,7 +2660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>17</v>
       </c>
@@ -2672,7 +2692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>17</v>
       </c>
@@ -2704,7 +2724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>18</v>
       </c>
@@ -2736,7 +2756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>18</v>
       </c>
@@ -2768,7 +2788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>19</v>
       </c>
@@ -2800,7 +2820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>20</v>
       </c>
@@ -2832,7 +2852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>21</v>
       </c>
@@ -2864,7 +2884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>22</v>
       </c>
@@ -2896,7 +2916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>23</v>
       </c>
@@ -2928,7 +2948,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>23</v>
       </c>
@@ -2960,7 +2980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>24</v>
       </c>
@@ -2998,47 +3018,60 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F9FDC1-14C6-4266-9073-6B882BAE9EDA}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86FC78B-DCD0-4746-9DAC-9D3D7F4C93B4}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
+        <v>194</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3047,11 +3080,60 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F9FDC1-14C6-4266-9073-6B882BAE9EDA}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72F2626-7535-47ED-A0A4-B25A1B06D345}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -3086,7 +3168,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>2316</v>
       </c>
@@ -3121,7 +3203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2317</v>
       </c>
@@ -3156,7 +3238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2318</v>
       </c>
@@ -3191,7 +3273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2327</v>
       </c>
@@ -3226,7 +3308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>2328</v>
       </c>
@@ -3261,7 +3343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>2329</v>
       </c>
@@ -3296,7 +3378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>2426</v>
       </c>
@@ -3331,7 +3413,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>2430</v>
       </c>
@@ -3366,7 +3448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2433</v>
       </c>
@@ -3401,7 +3483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>2434</v>
       </c>
@@ -3436,7 +3518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>2435</v>
       </c>
@@ -3471,7 +3553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>2439</v>
       </c>
@@ -3486,7 +3568,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="B14" t="s">
         <v>114</v>
       </c>
@@ -3495,7 +3577,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="B15">
         <v>1</v>
       </c>
@@ -3512,7 +3594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>2440</v>
       </c>
@@ -3547,7 +3629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>2441</v>
       </c>
@@ -3582,7 +3664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>2443</v>
       </c>
@@ -3617,7 +3699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>2444</v>
       </c>
@@ -3652,7 +3734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>2447</v>
       </c>
@@ -3687,7 +3769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>2448</v>
       </c>
@@ -3722,7 +3804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>2449</v>
       </c>
@@ -3757,7 +3839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>2450</v>
       </c>
@@ -3792,7 +3874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>2451</v>
       </c>
@@ -3827,7 +3909,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>2452</v>
       </c>
@@ -3862,7 +3944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>2453</v>
       </c>
@@ -3897,7 +3979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>2454</v>
       </c>
@@ -3932,7 +4014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>2455</v>
       </c>
@@ -3967,7 +4049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>2456</v>
       </c>
@@ -4002,7 +4084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>2457</v>
       </c>
@@ -4037,7 +4119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>2458</v>
       </c>
@@ -4072,7 +4154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>2459</v>
       </c>

--- a/database/Mater_issue_out.xlsx
+++ b/database/Mater_issue_out.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ecom\Ecome\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF66262-C1FD-41F0-AE8E-2723DE40E8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89C4203-B7A5-403F-87FE-FD2F7A37B1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_ACC_Master" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="203">
   <si>
     <t>TypeID</t>
   </si>
@@ -624,17 +621,41 @@
     <t>Flagdelete</t>
   </si>
   <si>
-    <t>Approved IT, PUR</t>
-  </si>
-  <si>
-    <t>('IT','PUR')</t>
+    <t>Phí Tiến Dũng</t>
+  </si>
+  <si>
+    <t>('PMD','SMT','PAPVN')</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hường</t>
+  </si>
+  <si>
+    <t>('PUS','COS','MCS','PMS')</t>
+  </si>
+  <si>
+    <t>Tran Hoang Hiep</t>
+  </si>
+  <si>
+    <t>('FA','PIS','FA-MW','Service part')</t>
+  </si>
+  <si>
+    <t>Nguyen The Anh</t>
+  </si>
+  <si>
+    <t>('FES','TED')</t>
+  </si>
+  <si>
+    <t>Dao thi khanh van</t>
+  </si>
+  <si>
+    <t>('QCD','OQC')</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,9 +1022,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0005190C-12A7-4AA2-B050-D4F6E798108D}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1043,7 +1064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1063,7 +1084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1083,7 +1104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1103,7 +1124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1123,7 +1144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1143,7 +1164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1163,7 +1184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1183,7 +1204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1203,7 +1224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1223,7 +1244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1243,7 +1264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1263,7 +1284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1283,7 +1304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1303,7 +1324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1323,7 +1344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1343,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1363,7 +1384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1383,7 +1404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1403,7 +1424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1423,7 +1444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1443,7 +1464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1463,7 +1484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1483,7 +1504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1511,9 +1532,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D651F0-8ED1-4701-BA6C-A1B31C35D92D}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1551,7 +1572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1589,7 +1610,7 @@
         <v>46037.427551967594</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1627,7 +1648,7 @@
         <v>46037.427552083333</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1673,9 +1694,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C07CBFB-1FCE-49A5-A1BD-2708DE2D3132}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1716,7 +1737,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>176</v>
       </c>
@@ -1757,7 +1778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>177</v>
       </c>
@@ -1798,7 +1819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>178</v>
       </c>
@@ -1839,7 +1860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>179</v>
       </c>
@@ -1888,20 +1909,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E041C3-B346-4B6E-B61E-D7486518563F}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="18.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="18.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="8.75" customWidth="1"/>
-    <col min="7" max="7" width="7.875" customWidth="1"/>
-    <col min="9" max="9" width="54.875" customWidth="1"/>
-    <col min="10" max="10" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
+    <col min="9" max="9" width="54.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1933,7 +1954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1965,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1994,7 +2015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2023,7 +2044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2052,7 +2073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2084,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2116,7 +2137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2148,7 +2169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2180,7 +2201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2212,7 +2233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -2244,7 +2265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2276,7 +2297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -2308,7 +2329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -2340,7 +2361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -2372,7 +2393,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -2404,7 +2425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -2436,7 +2457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>13</v>
       </c>
@@ -2468,7 +2489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>13</v>
       </c>
@@ -2500,7 +2521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>14</v>
       </c>
@@ -2532,7 +2553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>15</v>
       </c>
@@ -2564,7 +2585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>15</v>
       </c>
@@ -2596,7 +2617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>16</v>
       </c>
@@ -2628,7 +2649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>16</v>
       </c>
@@ -2660,7 +2681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
@@ -2692,7 +2713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>17</v>
       </c>
@@ -2724,7 +2745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>18</v>
       </c>
@@ -2756,7 +2777,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>18</v>
       </c>
@@ -2788,7 +2809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>19</v>
       </c>
@@ -2820,7 +2841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>20</v>
       </c>
@@ -2852,7 +2873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>21</v>
       </c>
@@ -2884,7 +2905,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>22</v>
       </c>
@@ -2916,7 +2937,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>23</v>
       </c>
@@ -2948,7 +2969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>23</v>
       </c>
@@ -2980,7 +3001,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>24</v>
       </c>
@@ -3019,10 +3040,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86FC78B-DCD0-4746-9DAC-9D3D7F4C93B4}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>189</v>
       </c>
@@ -3048,12 +3075,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
+      <c r="B2">
+        <v>2001822</v>
       </c>
       <c r="C2" t="s">
         <v>193</v>
@@ -3071,6 +3098,162 @@
         <v>32</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>2001822</v>
+      </c>
+      <c r="C5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2000032</v>
+      </c>
+      <c r="C6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2000182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2001278</v>
+      </c>
+      <c r="C8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2000174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -3082,9 +3265,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F9FDC1-14C6-4266-9073-6B882BAE9EDA}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -3098,7 +3281,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3112,7 +3295,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3131,9 +3314,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72F2626-7535-47ED-A0A4-B25A1B06D345}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -3168,7 +3351,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2316</v>
       </c>
@@ -3203,7 +3386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2317</v>
       </c>
@@ -3238,7 +3421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2318</v>
       </c>
@@ -3273,7 +3456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2327</v>
       </c>
@@ -3308,7 +3491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2328</v>
       </c>
@@ -3343,7 +3526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2329</v>
       </c>
@@ -3378,7 +3561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2426</v>
       </c>
@@ -3413,7 +3596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2430</v>
       </c>
@@ -3448,7 +3631,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2433</v>
       </c>
@@ -3483,7 +3666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2434</v>
       </c>
@@ -3518,7 +3701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2435</v>
       </c>
@@ -3553,7 +3736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2439</v>
       </c>
@@ -3568,7 +3751,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>114</v>
       </c>
@@ -3577,7 +3760,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1</v>
       </c>
@@ -3594,7 +3777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2440</v>
       </c>
@@ -3629,7 +3812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2441</v>
       </c>
@@ -3664,7 +3847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2443</v>
       </c>
@@ -3699,7 +3882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2444</v>
       </c>
@@ -3734,7 +3917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2447</v>
       </c>
@@ -3769,7 +3952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2448</v>
       </c>
@@ -3804,7 +3987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2449</v>
       </c>
@@ -3839,7 +4022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2450</v>
       </c>
@@ -3874,7 +4057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2451</v>
       </c>
@@ -3909,7 +4092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2452</v>
       </c>
@@ -3944,7 +4127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2453</v>
       </c>
@@ -3979,7 +4162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2454</v>
       </c>
@@ -4014,7 +4197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2455</v>
       </c>
@@ -4049,7 +4232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2456</v>
       </c>
@@ -4084,7 +4267,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2457</v>
       </c>
@@ -4119,7 +4302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2458</v>
       </c>
@@ -4154,7 +4337,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2459</v>
       </c>

--- a/database/Mater_issue_out.xlsx
+++ b/database/Mater_issue_out.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89C4203-B7A5-403F-87FE-FD2F7A37B1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4DAEDA-B64F-4A2C-9902-44F72E39017B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{863B0F70-79CD-441E-8E11-AA8262AC5FF9}"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_ACC_Master" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="tbl_UserDeptCombine" sheetId="7" r:id="rId5"/>
     <sheet name="tbl_User_checkPrice" sheetId="5" r:id="rId6"/>
     <sheet name="tbl_UserIssueRQ" sheetId="6" r:id="rId7"/>
+    <sheet name="mater_requst" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="341">
   <si>
     <t>TypeID</t>
   </si>
@@ -649,6 +650,420 @@
   </si>
   <si>
     <t>('QCD','OQC')</t>
+  </si>
+  <si>
+    <t>RequestNo</t>
+  </si>
+  <si>
+    <t>ItemDescription</t>
+  </si>
+  <si>
+    <t>MvType</t>
+  </si>
+  <si>
+    <t>MvName</t>
+  </si>
+  <si>
+    <t>VendorCode</t>
+  </si>
+  <si>
+    <t>CostCenter</t>
+  </si>
+  <si>
+    <t>IssueQty</t>
+  </si>
+  <si>
+    <t>UnitPrice_ST</t>
+  </si>
+  <si>
+    <t>Amount_ST</t>
+  </si>
+  <si>
+    <t>DateVoucher</t>
+  </si>
+  <si>
+    <t>CountryofOrigin</t>
+  </si>
+  <si>
+    <t>UserCreate</t>
+  </si>
+  <si>
+    <t>DateUpdate</t>
+  </si>
+  <si>
+    <t>CodeInchage_Issue</t>
+  </si>
+  <si>
+    <t>NameInchage_Issue</t>
+  </si>
+  <si>
+    <t>DateInchage_Issue</t>
+  </si>
+  <si>
+    <t>StatusInchage_Issue</t>
+  </si>
+  <si>
+    <t>CodeMGR_Issue</t>
+  </si>
+  <si>
+    <t>NameMGR_Issue</t>
+  </si>
+  <si>
+    <t>DateMGR_Issue</t>
+  </si>
+  <si>
+    <t>StatusMGR_Issue</t>
+  </si>
+  <si>
+    <t>CodeGM_Issue</t>
+  </si>
+  <si>
+    <t>NameGM_Issue</t>
+  </si>
+  <si>
+    <t>DateGM_Issue</t>
+  </si>
+  <si>
+    <t>StatusGM_Issue</t>
+  </si>
+  <si>
+    <t>NameACC_Check</t>
+  </si>
+  <si>
+    <t>CodeACC_Check</t>
+  </si>
+  <si>
+    <t>DateACC_Check</t>
+  </si>
+  <si>
+    <t>StatusACC_Check</t>
+  </si>
+  <si>
+    <t>CodeACC_MGR</t>
+  </si>
+  <si>
+    <t>NameACC_MGR</t>
+  </si>
+  <si>
+    <t>DateACC_MGR</t>
+  </si>
+  <si>
+    <t>StatusACC_MGR</t>
+  </si>
+  <si>
+    <t>CodeACC_GM</t>
+  </si>
+  <si>
+    <t>NameACC_GM</t>
+  </si>
+  <si>
+    <t>DateACC_GM</t>
+  </si>
+  <si>
+    <t>StatusACC_GM</t>
+  </si>
+  <si>
+    <t>CodeInchage_Out</t>
+  </si>
+  <si>
+    <t>NameInchage_Out</t>
+  </si>
+  <si>
+    <t>DateInchage_Out</t>
+  </si>
+  <si>
+    <t>StatusInchage_Out</t>
+  </si>
+  <si>
+    <t>CodeMGR_Out</t>
+  </si>
+  <si>
+    <t>NameMGR_Out</t>
+  </si>
+  <si>
+    <t>DateMGR_Out</t>
+  </si>
+  <si>
+    <t>StatusMGR_Out</t>
+  </si>
+  <si>
+    <t>CodeGM_Out</t>
+  </si>
+  <si>
+    <t>NameGM_Out</t>
+  </si>
+  <si>
+    <t>DateGM_Out</t>
+  </si>
+  <si>
+    <t>StatusGM_Out</t>
+  </si>
+  <si>
+    <t>Status_RQ</t>
+  </si>
+  <si>
+    <t>Status_IVoice</t>
+  </si>
+  <si>
+    <t>Status_Delete</t>
+  </si>
+  <si>
+    <t>RQDeptID</t>
+  </si>
+  <si>
+    <t>Insert_Date</t>
+  </si>
+  <si>
+    <t>CDS_No</t>
+  </si>
+  <si>
+    <t>CDS_Date</t>
+  </si>
+  <si>
+    <t>User_Approved_OutSAP</t>
+  </si>
+  <si>
+    <t>Name_Approved_OutSAP</t>
+  </si>
+  <si>
+    <t>Status_Approved_OutSAP</t>
+  </si>
+  <si>
+    <t>Date_Approved_OutSAP</t>
+  </si>
+  <si>
+    <t>SanctionName</t>
+  </si>
+  <si>
+    <t>Flag_price_sap</t>
+  </si>
+  <si>
+    <t>Type_Rosh_Halb</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>NameCode</t>
+  </si>
+  <si>
+    <t>DocumentNo</t>
+  </si>
+  <si>
+    <t>Export_flag_98</t>
+  </si>
+  <si>
+    <t>Export_flag_99</t>
+  </si>
+  <si>
+    <t>Export_flag_outscrap</t>
+  </si>
+  <si>
+    <t>TypeSapPMS</t>
+  </si>
+  <si>
+    <t>Linkfile</t>
+  </si>
+  <si>
+    <t>CommentPMS</t>
+  </si>
+  <si>
+    <t>Export_flag_subscrap</t>
+  </si>
+  <si>
+    <t>Satatu_tranferPMS</t>
+  </si>
+  <si>
+    <t>TypeOutSap</t>
+  </si>
+  <si>
+    <t>Status_Finish_PMS</t>
+  </si>
+  <si>
+    <t>RQA-PUS-0526-206</t>
+  </si>
+  <si>
+    <t>PNHX1391ZA/V1</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>VR01</t>
+  </si>
+  <si>
+    <t>VE002</t>
+  </si>
+  <si>
+    <t>MA6100</t>
+  </si>
+  <si>
+    <t>Trần Thanh Riễm</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Roh</t>
+  </si>
+  <si>
+    <t>Shortage part</t>
+  </si>
+  <si>
+    <t>PUS_Door Phone</t>
+  </si>
+  <si>
+    <t>Sloc98</t>
+  </si>
+  <si>
+    <t>L0AA02A00087</t>
+  </si>
+  <si>
+    <t>VJ005</t>
+  </si>
+  <si>
+    <t>PNLB2452XA-AP</t>
+  </si>
+  <si>
+    <t>VE055</t>
+  </si>
+  <si>
+    <t>PNLB2848ZA-5N</t>
+  </si>
+  <si>
+    <t>VF170</t>
+  </si>
+  <si>
+    <t>H04288U0AP</t>
+  </si>
+  <si>
+    <t>VE121</t>
+  </si>
+  <si>
+    <t>MAM100</t>
+  </si>
+  <si>
+    <t>PUS_MICROWAVE</t>
+  </si>
+  <si>
+    <t>K0H1BA000138</t>
+  </si>
+  <si>
+    <t>VB014Y</t>
+  </si>
+  <si>
+    <t>PUKV1049ZA/V1</t>
+  </si>
+  <si>
+    <t>VE01</t>
+  </si>
+  <si>
+    <t>MAS100</t>
+  </si>
+  <si>
+    <t>9S98</t>
+  </si>
+  <si>
+    <t>PUS_SOUND BIZ</t>
+  </si>
+  <si>
+    <t>PGKM1235XA/C1</t>
+  </si>
+  <si>
+    <t>VE100</t>
+  </si>
+  <si>
+    <t>PGKV1524XA/C1</t>
+  </si>
+  <si>
+    <t>PUMK1001ZA/V2</t>
+  </si>
+  <si>
+    <t>VE077</t>
+  </si>
+  <si>
+    <t>PGGE1076XA/C1</t>
+  </si>
+  <si>
+    <t>PGGG1023ZA/C1</t>
+  </si>
+  <si>
+    <t>PGMH2237ZA/C1</t>
+  </si>
+  <si>
+    <t>XZB25X35A04/V1</t>
+  </si>
+  <si>
+    <t>VE125</t>
+  </si>
+  <si>
+    <t>PGGP1209ZA/C1</t>
+  </si>
+  <si>
+    <t>PUHX1019YA/V1</t>
+  </si>
+  <si>
+    <t>VE085</t>
+  </si>
+  <si>
+    <t>XSN26+8FNV1</t>
+  </si>
+  <si>
+    <t>VE026</t>
+  </si>
+  <si>
+    <t>PUPE1001ZA/V2</t>
+  </si>
+  <si>
+    <t>PGPD1315ZA/V7</t>
+  </si>
+  <si>
+    <t>VE041</t>
+  </si>
+  <si>
+    <t>PUHR1024ZA/V1</t>
+  </si>
+  <si>
+    <t>VE076</t>
+  </si>
+  <si>
+    <t>PGHX1407ZA/C1</t>
+  </si>
+  <si>
+    <t>FROM [Issue_MaterialInOut].[dbo].[tbl_RQ_MaterialIssue] where RequestNo='RQA-PUS-0526-206'</t>
+  </si>
+  <si>
+    <t>UnitPrice_AC</t>
+  </si>
+  <si>
+    <t>Amount_AC</t>
+  </si>
+  <si>
+    <t>RQB-PUS-0526-47</t>
+  </si>
+  <si>
+    <t>PNGP1418SC2W252/V2</t>
+  </si>
+  <si>
+    <t>VF190</t>
+  </si>
+  <si>
+    <t>Claim Scrap Material/VF190/PUSVR26-3170</t>
+  </si>
+  <si>
+    <t>PNJK1370ZA/V1</t>
+  </si>
+  <si>
+    <t>VB012</t>
+  </si>
+  <si>
+    <t>Claim Scrap Material/VB012/ PUSVR26-3183</t>
+  </si>
+  <si>
+    <t>FROM [Issue_MaterialInOut].[dbo].[tbl_RQ_MaterialIssueB] where RequestNo='RQB-PUS-0526-47'</t>
   </si>
 </sst>
 </file>
@@ -684,9 +1099,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4375,4 +4791,6110 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC6B7C1-25F7-46DD-BC9E-F01D5FF6DB7A}">
+  <dimension ref="A1:CG29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M2" t="s">
+        <v>210</v>
+      </c>
+      <c r="N2" t="s">
+        <v>211</v>
+      </c>
+      <c r="O2" t="s">
+        <v>212</v>
+      </c>
+      <c r="P2" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" t="s">
+        <v>214</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
+        <v>215</v>
+      </c>
+      <c r="U2" t="s">
+        <v>216</v>
+      </c>
+      <c r="V2" t="s">
+        <v>217</v>
+      </c>
+      <c r="W2" t="s">
+        <v>218</v>
+      </c>
+      <c r="X2" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>225</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>231</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>233</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>235</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>237</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>245</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>247</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>248</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>249</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>250</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>252</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>253</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>254</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>256</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>257</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>258</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>260</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>261</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>262</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>263</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>264</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>265</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>267</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>268</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>269</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>270</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>271</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>272</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>273</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>274</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>275</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>276</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>277</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>12239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>201</v>
+      </c>
+      <c r="G3" t="s">
+        <v>281</v>
+      </c>
+      <c r="H3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K3">
+        <v>1198</v>
+      </c>
+      <c r="L3">
+        <v>2000</v>
+      </c>
+      <c r="M3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>25</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R3">
+        <v>2000519</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3">
+        <v>2000519</v>
+      </c>
+      <c r="V3" t="s">
+        <v>285</v>
+      </c>
+      <c r="W3" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>46171.725354050926</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>12240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>201</v>
+      </c>
+      <c r="G4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K4">
+        <v>1198</v>
+      </c>
+      <c r="L4">
+        <v>73</v>
+      </c>
+      <c r="M4">
+        <v>0.1275</v>
+      </c>
+      <c r="N4">
+        <v>9.3074999999999992</v>
+      </c>
+      <c r="O4" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R4">
+        <v>2000519</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4">
+        <v>2000519</v>
+      </c>
+      <c r="V4" t="s">
+        <v>285</v>
+      </c>
+      <c r="W4" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X4" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>46171.725354050926</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB4">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>12241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>201</v>
+      </c>
+      <c r="G5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I5" t="s">
+        <v>295</v>
+      </c>
+      <c r="J5" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5">
+        <v>1198</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>0.6885</v>
+      </c>
+      <c r="N5">
+        <v>2.754</v>
+      </c>
+      <c r="O5" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R5">
+        <v>2000519</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5">
+        <v>2000519</v>
+      </c>
+      <c r="V5" t="s">
+        <v>285</v>
+      </c>
+      <c r="W5" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X5" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>46171.725354050926</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB5">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>12242</v>
+      </c>
+      <c r="B6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>201</v>
+      </c>
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I6" t="s">
+        <v>297</v>
+      </c>
+      <c r="J6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6">
+        <v>1198</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="N6">
+        <v>0.94979999999999998</v>
+      </c>
+      <c r="O6" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R6">
+        <v>2000519</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6">
+        <v>2000519</v>
+      </c>
+      <c r="V6" t="s">
+        <v>285</v>
+      </c>
+      <c r="W6" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X6" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>46171.725354050926</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB6">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>12243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>201</v>
+      </c>
+      <c r="G7" t="s">
+        <v>281</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>299</v>
+      </c>
+      <c r="J7" t="s">
+        <v>300</v>
+      </c>
+      <c r="K7">
+        <v>6198</v>
+      </c>
+      <c r="L7">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>0.13439999999999999</v>
+      </c>
+      <c r="N7">
+        <v>6.72</v>
+      </c>
+      <c r="O7" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R7">
+        <v>2000519</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7">
+        <v>2000519</v>
+      </c>
+      <c r="V7" t="s">
+        <v>285</v>
+      </c>
+      <c r="W7" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X7" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI7" s="1">
+        <v>46171.725354050926</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>301</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB7">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>12244</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>201</v>
+      </c>
+      <c r="G8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>303</v>
+      </c>
+      <c r="J8" t="s">
+        <v>300</v>
+      </c>
+      <c r="K8">
+        <v>6198</v>
+      </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
+      <c r="M8">
+        <v>2.759E-2</v>
+      </c>
+      <c r="N8">
+        <v>1.1035999999999999</v>
+      </c>
+      <c r="O8" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R8">
+        <v>2000519</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8">
+        <v>2000519</v>
+      </c>
+      <c r="V8" t="s">
+        <v>285</v>
+      </c>
+      <c r="W8" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X8" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI8" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>301</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB8">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD8" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>12245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>201</v>
+      </c>
+      <c r="G9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" t="s">
+        <v>305</v>
+      </c>
+      <c r="I9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J9" t="s">
+        <v>306</v>
+      </c>
+      <c r="K9" t="s">
+        <v>307</v>
+      </c>
+      <c r="L9">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="N9">
+        <v>4.41</v>
+      </c>
+      <c r="O9" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R9">
+        <v>2000519</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9">
+        <v>2000519</v>
+      </c>
+      <c r="V9" t="s">
+        <v>285</v>
+      </c>
+      <c r="W9" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X9" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB9">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>12246</v>
+      </c>
+      <c r="B10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>201</v>
+      </c>
+      <c r="G10" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" t="s">
+        <v>305</v>
+      </c>
+      <c r="I10" t="s">
+        <v>310</v>
+      </c>
+      <c r="J10" t="s">
+        <v>306</v>
+      </c>
+      <c r="K10" t="s">
+        <v>307</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>3.4712000000000001</v>
+      </c>
+      <c r="N10">
+        <v>3.4712000000000001</v>
+      </c>
+      <c r="O10" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R10">
+        <v>2000519</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10">
+        <v>2000519</v>
+      </c>
+      <c r="V10" t="s">
+        <v>285</v>
+      </c>
+      <c r="W10" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X10" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI10" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB10">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>12247</v>
+      </c>
+      <c r="B11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>201</v>
+      </c>
+      <c r="G11" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" t="s">
+        <v>310</v>
+      </c>
+      <c r="J11" t="s">
+        <v>306</v>
+      </c>
+      <c r="K11" t="s">
+        <v>307</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>3.4533</v>
+      </c>
+      <c r="N11">
+        <v>3.4533</v>
+      </c>
+      <c r="O11" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R11">
+        <v>2000519</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11">
+        <v>2000519</v>
+      </c>
+      <c r="V11" t="s">
+        <v>285</v>
+      </c>
+      <c r="W11" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X11" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI11" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA11" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB11">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD11" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12248</v>
+      </c>
+      <c r="B12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>201</v>
+      </c>
+      <c r="G12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H12" t="s">
+        <v>305</v>
+      </c>
+      <c r="I12" t="s">
+        <v>313</v>
+      </c>
+      <c r="J12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K12" t="s">
+        <v>307</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>3.33</v>
+      </c>
+      <c r="N12">
+        <v>3.33</v>
+      </c>
+      <c r="O12" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R12">
+        <v>2000519</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12">
+        <v>2000519</v>
+      </c>
+      <c r="V12" t="s">
+        <v>285</v>
+      </c>
+      <c r="W12" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X12" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI12" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB12">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" t="s">
+        <v>314</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>201</v>
+      </c>
+      <c r="G13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H13" t="s">
+        <v>305</v>
+      </c>
+      <c r="I13" t="s">
+        <v>310</v>
+      </c>
+      <c r="J13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K13" t="s">
+        <v>307</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="N13">
+        <v>2.343</v>
+      </c>
+      <c r="O13" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R13">
+        <v>2000519</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13">
+        <v>2000519</v>
+      </c>
+      <c r="V13" t="s">
+        <v>285</v>
+      </c>
+      <c r="W13" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X13" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI13" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU13" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ13" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA13" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB13">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD13" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12250</v>
+      </c>
+      <c r="B14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" t="s">
+        <v>315</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>201</v>
+      </c>
+      <c r="G14" t="s">
+        <v>281</v>
+      </c>
+      <c r="H14" t="s">
+        <v>305</v>
+      </c>
+      <c r="I14" t="s">
+        <v>310</v>
+      </c>
+      <c r="J14" t="s">
+        <v>306</v>
+      </c>
+      <c r="K14" t="s">
+        <v>307</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>2.0827</v>
+      </c>
+      <c r="N14">
+        <v>2.0827</v>
+      </c>
+      <c r="O14" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R14">
+        <v>2000519</v>
+      </c>
+      <c r="S14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14">
+        <v>2000519</v>
+      </c>
+      <c r="V14" t="s">
+        <v>285</v>
+      </c>
+      <c r="W14" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X14" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI14" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ14" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA14" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB14">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD14" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>12251</v>
+      </c>
+      <c r="B15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" t="s">
+        <v>316</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>201</v>
+      </c>
+      <c r="G15" t="s">
+        <v>281</v>
+      </c>
+      <c r="H15" t="s">
+        <v>305</v>
+      </c>
+      <c r="I15" t="s">
+        <v>310</v>
+      </c>
+      <c r="J15" t="s">
+        <v>306</v>
+      </c>
+      <c r="K15" t="s">
+        <v>307</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
+        <v>0.40039999999999998</v>
+      </c>
+      <c r="N15">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="O15" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R15">
+        <v>2000519</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15">
+        <v>2000519</v>
+      </c>
+      <c r="V15" t="s">
+        <v>285</v>
+      </c>
+      <c r="W15" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X15" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI15" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT15" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU15" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA15" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB15">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD15" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>12252</v>
+      </c>
+      <c r="B16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>201</v>
+      </c>
+      <c r="G16" t="s">
+        <v>281</v>
+      </c>
+      <c r="H16" t="s">
+        <v>305</v>
+      </c>
+      <c r="I16" t="s">
+        <v>318</v>
+      </c>
+      <c r="J16" t="s">
+        <v>306</v>
+      </c>
+      <c r="K16" t="s">
+        <v>307</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="N16">
+        <v>1.65</v>
+      </c>
+      <c r="O16" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R16">
+        <v>2000519</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16">
+        <v>2000519</v>
+      </c>
+      <c r="V16" t="s">
+        <v>285</v>
+      </c>
+      <c r="W16" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X16" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI16" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU16" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA16" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB16">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>12253</v>
+      </c>
+      <c r="B17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>201</v>
+      </c>
+      <c r="G17" t="s">
+        <v>281</v>
+      </c>
+      <c r="H17" t="s">
+        <v>305</v>
+      </c>
+      <c r="I17" t="s">
+        <v>310</v>
+      </c>
+      <c r="J17" t="s">
+        <v>306</v>
+      </c>
+      <c r="K17" t="s">
+        <v>307</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1.3885000000000001</v>
+      </c>
+      <c r="N17">
+        <v>1.3885000000000001</v>
+      </c>
+      <c r="O17" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R17">
+        <v>2000519</v>
+      </c>
+      <c r="S17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17">
+        <v>2000519</v>
+      </c>
+      <c r="V17" t="s">
+        <v>285</v>
+      </c>
+      <c r="W17" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X17" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI17" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS17" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT17" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU17" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ17" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA17" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB17">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD17" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C18" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>201</v>
+      </c>
+      <c r="G18" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" t="s">
+        <v>321</v>
+      </c>
+      <c r="J18" t="s">
+        <v>306</v>
+      </c>
+      <c r="K18" t="s">
+        <v>307</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
+      <c r="M18">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="N18">
+        <v>0.90239999999999998</v>
+      </c>
+      <c r="O18" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R18">
+        <v>2000519</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18">
+        <v>2000519</v>
+      </c>
+      <c r="V18" t="s">
+        <v>285</v>
+      </c>
+      <c r="W18" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X18" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI18" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS18" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT18" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA18" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB18">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>12255</v>
+      </c>
+      <c r="B19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>201</v>
+      </c>
+      <c r="G19" t="s">
+        <v>281</v>
+      </c>
+      <c r="H19" t="s">
+        <v>305</v>
+      </c>
+      <c r="I19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J19" t="s">
+        <v>306</v>
+      </c>
+      <c r="K19" t="s">
+        <v>307</v>
+      </c>
+      <c r="L19">
+        <v>240</v>
+      </c>
+      <c r="M19">
+        <v>2.5200000000000001E-3</v>
+      </c>
+      <c r="N19">
+        <v>0.6048</v>
+      </c>
+      <c r="O19" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R19">
+        <v>2000519</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19">
+        <v>2000519</v>
+      </c>
+      <c r="V19" t="s">
+        <v>285</v>
+      </c>
+      <c r="W19" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X19" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI19" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT19" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ19" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB19">
+        <v>0</v>
+      </c>
+      <c r="CC19" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>12256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" t="s">
+        <v>324</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>201</v>
+      </c>
+      <c r="G20" t="s">
+        <v>281</v>
+      </c>
+      <c r="H20" t="s">
+        <v>305</v>
+      </c>
+      <c r="I20" t="s">
+        <v>318</v>
+      </c>
+      <c r="J20" t="s">
+        <v>306</v>
+      </c>
+      <c r="K20" t="s">
+        <v>307</v>
+      </c>
+      <c r="L20">
+        <v>20</v>
+      </c>
+      <c r="M20">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="N20">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="O20" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R20">
+        <v>2000519</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20">
+        <v>2000519</v>
+      </c>
+      <c r="V20" t="s">
+        <v>285</v>
+      </c>
+      <c r="W20" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X20" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI20" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT20" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU20" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ20" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA20" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB20">
+        <v>0</v>
+      </c>
+      <c r="CC20" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD20" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>12257</v>
+      </c>
+      <c r="B21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>201</v>
+      </c>
+      <c r="G21" t="s">
+        <v>281</v>
+      </c>
+      <c r="H21" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" t="s">
+        <v>326</v>
+      </c>
+      <c r="J21" t="s">
+        <v>306</v>
+      </c>
+      <c r="K21" t="s">
+        <v>307</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="O21" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R21">
+        <v>2000519</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21">
+        <v>2000519</v>
+      </c>
+      <c r="V21" t="s">
+        <v>285</v>
+      </c>
+      <c r="W21" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X21" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI21" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT21" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU21" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ21" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB21">
+        <v>0</v>
+      </c>
+      <c r="CC21" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD21" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>12258</v>
+      </c>
+      <c r="B22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>201</v>
+      </c>
+      <c r="G22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H22" t="s">
+        <v>305</v>
+      </c>
+      <c r="I22" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" t="s">
+        <v>306</v>
+      </c>
+      <c r="K22" t="s">
+        <v>307</v>
+      </c>
+      <c r="L22">
+        <v>14</v>
+      </c>
+      <c r="M22">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O22" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R22">
+        <v>2000519</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22">
+        <v>2000519</v>
+      </c>
+      <c r="V22" t="s">
+        <v>285</v>
+      </c>
+      <c r="W22" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X22" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE22" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI22" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN22" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS22" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT22" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU22" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ22" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA22" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB22">
+        <v>0</v>
+      </c>
+      <c r="CC22" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD22" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>12259</v>
+      </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>201</v>
+      </c>
+      <c r="G23" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" t="s">
+        <v>310</v>
+      </c>
+      <c r="J23" t="s">
+        <v>306</v>
+      </c>
+      <c r="K23" t="s">
+        <v>307</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>0.02</v>
+      </c>
+      <c r="N23">
+        <v>0.04</v>
+      </c>
+      <c r="O23" s="2">
+        <v>46059</v>
+      </c>
+      <c r="R23">
+        <v>2000519</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23">
+        <v>2000519</v>
+      </c>
+      <c r="V23" t="s">
+        <v>285</v>
+      </c>
+      <c r="W23" s="1">
+        <v>46171.725739201385</v>
+      </c>
+      <c r="X23" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>287</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG23" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH23" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI23" s="1">
+        <v>46171.725354085647</v>
+      </c>
+      <c r="BJ23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="s">
+        <v>288</v>
+      </c>
+      <c r="BS23" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT23" t="s">
+        <v>308</v>
+      </c>
+      <c r="BU23" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ23" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA23" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB23">
+        <v>0</v>
+      </c>
+      <c r="CC23" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD23" t="s">
+        <v>51</v>
+      </c>
+      <c r="CE23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
+        <v>207</v>
+      </c>
+      <c r="J27" t="s">
+        <v>208</v>
+      </c>
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>209</v>
+      </c>
+      <c r="M27" t="s">
+        <v>210</v>
+      </c>
+      <c r="N27" t="s">
+        <v>211</v>
+      </c>
+      <c r="O27" t="s">
+        <v>331</v>
+      </c>
+      <c r="P27" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>212</v>
+      </c>
+      <c r="R27" t="s">
+        <v>213</v>
+      </c>
+      <c r="S27" t="s">
+        <v>47</v>
+      </c>
+      <c r="T27" t="s">
+        <v>214</v>
+      </c>
+      <c r="U27" t="s">
+        <v>27</v>
+      </c>
+      <c r="V27" t="s">
+        <v>215</v>
+      </c>
+      <c r="W27" t="s">
+        <v>216</v>
+      </c>
+      <c r="X27" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>220</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>223</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>224</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>225</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>226</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>227</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>228</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>229</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>231</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>232</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>233</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>234</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>235</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>236</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>237</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>238</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU27" t="s">
+        <v>240</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>241</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>242</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>243</v>
+      </c>
+      <c r="AY27" t="s">
+        <v>244</v>
+      </c>
+      <c r="AZ27" t="s">
+        <v>245</v>
+      </c>
+      <c r="BA27" t="s">
+        <v>246</v>
+      </c>
+      <c r="BB27" t="s">
+        <v>247</v>
+      </c>
+      <c r="BC27" t="s">
+        <v>248</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>249</v>
+      </c>
+      <c r="BE27" t="s">
+        <v>250</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>251</v>
+      </c>
+      <c r="BG27" t="s">
+        <v>252</v>
+      </c>
+      <c r="BH27" t="s">
+        <v>253</v>
+      </c>
+      <c r="BI27" t="s">
+        <v>254</v>
+      </c>
+      <c r="BJ27" t="s">
+        <v>255</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>256</v>
+      </c>
+      <c r="BL27" t="s">
+        <v>257</v>
+      </c>
+      <c r="BM27" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN27" t="s">
+        <v>259</v>
+      </c>
+      <c r="BO27" t="s">
+        <v>260</v>
+      </c>
+      <c r="BP27" t="s">
+        <v>261</v>
+      </c>
+      <c r="BQ27" t="s">
+        <v>262</v>
+      </c>
+      <c r="BR27" t="s">
+        <v>263</v>
+      </c>
+      <c r="BS27" t="s">
+        <v>264</v>
+      </c>
+      <c r="BT27" t="s">
+        <v>265</v>
+      </c>
+      <c r="BU27" t="s">
+        <v>266</v>
+      </c>
+      <c r="BV27" t="s">
+        <v>267</v>
+      </c>
+      <c r="BW27" t="s">
+        <v>268</v>
+      </c>
+      <c r="BX27" t="s">
+        <v>269</v>
+      </c>
+      <c r="BY27" t="s">
+        <v>270</v>
+      </c>
+      <c r="BZ27" t="s">
+        <v>271</v>
+      </c>
+      <c r="CA27" t="s">
+        <v>272</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>273</v>
+      </c>
+      <c r="CC27" t="s">
+        <v>274</v>
+      </c>
+      <c r="CD27" t="s">
+        <v>275</v>
+      </c>
+      <c r="CE27" t="s">
+        <v>276</v>
+      </c>
+      <c r="CF27" t="s">
+        <v>277</v>
+      </c>
+      <c r="CG27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2348</v>
+      </c>
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>201</v>
+      </c>
+      <c r="G28" t="s">
+        <v>281</v>
+      </c>
+      <c r="H28" t="s">
+        <v>282</v>
+      </c>
+      <c r="I28" t="s">
+        <v>335</v>
+      </c>
+      <c r="J28" t="s">
+        <v>284</v>
+      </c>
+      <c r="K28">
+        <v>1198</v>
+      </c>
+      <c r="L28">
+        <v>800</v>
+      </c>
+      <c r="M28">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="N28">
+        <v>562.4</v>
+      </c>
+      <c r="O28">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="P28">
+        <v>562.4</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>46059</v>
+      </c>
+      <c r="T28">
+        <v>2000519</v>
+      </c>
+      <c r="U28" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" t="s">
+        <v>32</v>
+      </c>
+      <c r="W28">
+        <v>2000519</v>
+      </c>
+      <c r="X28" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>46171.725075543982</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG28" t="s">
+        <v>287</v>
+      </c>
+      <c r="BH28" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI28" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ28" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK28" s="1">
+        <v>46171.724520520831</v>
+      </c>
+      <c r="BL28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BO28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP28" t="s">
+        <v>287</v>
+      </c>
+      <c r="BQ28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="s">
+        <v>288</v>
+      </c>
+      <c r="BU28" t="s">
+        <v>336</v>
+      </c>
+      <c r="BV28" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW28" t="s">
+        <v>32</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="s">
+        <v>291</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>32</v>
+      </c>
+      <c r="CC28" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD28">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF28" t="s">
+        <v>51</v>
+      </c>
+      <c r="CG28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2349</v>
+      </c>
+      <c r="B29" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" t="s">
+        <v>337</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>201</v>
+      </c>
+      <c r="G29" t="s">
+        <v>281</v>
+      </c>
+      <c r="H29" t="s">
+        <v>282</v>
+      </c>
+      <c r="I29" t="s">
+        <v>338</v>
+      </c>
+      <c r="J29" t="s">
+        <v>284</v>
+      </c>
+      <c r="K29">
+        <v>1198</v>
+      </c>
+      <c r="L29">
+        <v>130</v>
+      </c>
+      <c r="M29">
+        <v>0.13569999999999999</v>
+      </c>
+      <c r="N29">
+        <v>17.640999999999998</v>
+      </c>
+      <c r="O29">
+        <v>0.13569999999999999</v>
+      </c>
+      <c r="P29">
+        <v>17.640999999999998</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>46059</v>
+      </c>
+      <c r="T29">
+        <v>2000519</v>
+      </c>
+      <c r="U29" t="s">
+        <v>32</v>
+      </c>
+      <c r="V29" t="s">
+        <v>32</v>
+      </c>
+      <c r="W29">
+        <v>2000519</v>
+      </c>
+      <c r="X29" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>46171.725075543982</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG29" t="s">
+        <v>287</v>
+      </c>
+      <c r="BH29" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI29" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ29" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK29" s="1">
+        <v>46171.724520520831</v>
+      </c>
+      <c r="BL29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BO29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP29" t="s">
+        <v>287</v>
+      </c>
+      <c r="BQ29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="s">
+        <v>288</v>
+      </c>
+      <c r="BU29" t="s">
+        <v>339</v>
+      </c>
+      <c r="BV29" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="s">
+        <v>291</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CC29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CD29">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF29" t="s">
+        <v>51</v>
+      </c>
+      <c r="CG29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>